--- a/Ecommerce_MFQ_TestCases.xlsx
+++ b/Ecommerce_MFQ_TestCases.xlsx
@@ -112,7 +112,8 @@
     <t>Pending Shipment Order Completes Shipment Transition</t>
   </si>
   <si>
-    <t>订单待发货、库存正常、WMS 服务可用</t>
+    <t xml:space="preserve">
+Orders are pending shipment, inventory is normal, and WMS service is available.</t>
   </si>
   <si>
     <t>1. System issues shipment instruction
